--- a/VerveStacks_NZL/SysSettings.xlsx
+++ b/VerveStacks_NZL/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CBFEDD-6A25-4292-B172-CF148FBF6F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF06CC15-B1A6-44B9-8B4B-5F817D87BC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="219">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -680,6 +680,21 @@
   </si>
   <si>
     <t>set</t>
+  </si>
+  <si>
+    <t>elc_spv-NZL</t>
+  </si>
+  <si>
+    <t>solar electricity generation</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>elc_won-NZL</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation</t>
   </si>
 </sst>
 </file>
@@ -3181,6 +3196,24 @@
       <c r="E5" t="s">
         <v>18</v>
       </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>214</v>
+      </c>
+      <c r="O5" t="s">
+        <v>215</v>
+      </c>
+      <c r="P5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" t="s">
@@ -3191,6 +3224,24 @@
       </c>
       <c r="E6" t="s">
         <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" t="s">
+        <v>217</v>
+      </c>
+      <c r="O6" t="s">
+        <v>218</v>
+      </c>
+      <c r="P6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R6" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:18">

--- a/VerveStacks_NZL/SysSettings.xlsx
+++ b/VerveStacks_NZL/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF06CC15-B1A6-44B9-8B4B-5F817D87BC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D72A1C0-EE3B-4C0B-B780-E8ECC9D3E09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -689,6 +689,12 @@
   </si>
   <si>
     <t>TWh</t>
+  </si>
+  <si>
+    <t>elc_wof-NZL</t>
+  </si>
+  <si>
+    <t>offshore wind electricity generation</t>
   </si>
   <si>
     <t>elc_won-NZL</t>
@@ -3254,6 +3260,24 @@
       <c r="E7" t="s">
         <v>18</v>
       </c>
+      <c r="M7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O7" t="s">
+        <v>220</v>
+      </c>
+      <c r="P7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="8" spans="2:18">
       <c r="B8" t="s">

--- a/VerveStacks_NZL/SysSettings.xlsx
+++ b/VerveStacks_NZL/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D72A1C0-EE3B-4C0B-B780-E8ECC9D3E09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0022FD2-4A83-4F81-A236-E31067D11416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL/SysSettings.xlsx
+++ b/VerveStacks_NZL/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0022FD2-4A83-4F81-A236-E31067D11416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCA114-0F1A-45CF-8753-9908B0F82CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="343">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -682,25 +682,391 @@
     <t>set</t>
   </si>
   <si>
-    <t>elc_spv-NZL</t>
-  </si>
-  <si>
-    <t>solar electricity generation</t>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_wof-NZL</t>
-  </si>
-  <si>
-    <t>offshore wind electricity generation</t>
-  </si>
-  <si>
-    <t>elc_won-NZL</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation</t>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 15</t>
   </si>
 </sst>
 </file>
@@ -3116,7 +3482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R24"/>
+  <dimension ref="B3:R68"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -3289,6 +3655,24 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O8" t="s">
+        <v>222</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="9" spans="2:18">
       <c r="B9" t="s">
@@ -3300,6 +3684,24 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O9" t="s">
+        <v>224</v>
+      </c>
+      <c r="P9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="10" spans="2:18">
       <c r="B10" t="s">
@@ -3311,6 +3713,24 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" t="s">
@@ -3322,6 +3742,24 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>227</v>
+      </c>
+      <c r="O11" t="s">
+        <v>228</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" t="s">
@@ -3333,6 +3771,24 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>229</v>
+      </c>
+      <c r="O12" t="s">
+        <v>230</v>
+      </c>
+      <c r="P12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" t="s">
@@ -3344,6 +3800,24 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" t="s">
+        <v>232</v>
+      </c>
+      <c r="P13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
@@ -3358,6 +3832,24 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" t="s">
+        <v>234</v>
+      </c>
+      <c r="P14" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="15" spans="2:18">
       <c r="B15" t="s">
@@ -3372,6 +3864,24 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" t="s">
+        <v>236</v>
+      </c>
+      <c r="P15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="16" spans="2:18">
       <c r="B16" t="s">
@@ -3395,8 +3905,26 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>237</v>
+      </c>
+      <c r="O16" t="s">
+        <v>238</v>
+      </c>
+      <c r="P16" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -3409,8 +3937,26 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17" t="s">
+        <v>240</v>
+      </c>
+      <c r="P17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3423,8 +3969,26 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>241</v>
+      </c>
+      <c r="O18" t="s">
+        <v>242</v>
+      </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3437,8 +4001,26 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>243</v>
+      </c>
+      <c r="O19" t="s">
+        <v>244</v>
+      </c>
+      <c r="P19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3451,8 +4033,26 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P20" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -3471,8 +4071,26 @@
       <c r="G21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="M21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>247</v>
+      </c>
+      <c r="O21" t="s">
+        <v>248</v>
+      </c>
+      <c r="P21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>193</v>
       </c>
@@ -3485,8 +4103,26 @@
       <c r="E22" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s">
+        <v>250</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>193</v>
       </c>
@@ -3496,8 +4132,26 @@
       <c r="E23" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>251</v>
+      </c>
+      <c r="O23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>193</v>
       </c>
@@ -3506,6 +4160,904 @@
       </c>
       <c r="E24" t="s">
         <v>196</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" t="s">
+        <v>254</v>
+      </c>
+      <c r="P24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="M25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>255</v>
+      </c>
+      <c r="O25" t="s">
+        <v>256</v>
+      </c>
+      <c r="P25" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="M26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>257</v>
+      </c>
+      <c r="O26" t="s">
+        <v>258</v>
+      </c>
+      <c r="P26" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="M27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>259</v>
+      </c>
+      <c r="O27" t="s">
+        <v>260</v>
+      </c>
+      <c r="P27" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>261</v>
+      </c>
+      <c r="O28" t="s">
+        <v>262</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>263</v>
+      </c>
+      <c r="O29" t="s">
+        <v>264</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="M30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" t="s">
+        <v>266</v>
+      </c>
+      <c r="P30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>267</v>
+      </c>
+      <c r="O31" t="s">
+        <v>268</v>
+      </c>
+      <c r="P31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" t="s">
+        <v>270</v>
+      </c>
+      <c r="P32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="13:18">
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s">
+        <v>272</v>
+      </c>
+      <c r="P33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="13:18">
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>273</v>
+      </c>
+      <c r="O34" t="s">
+        <v>274</v>
+      </c>
+      <c r="P34" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="13:18">
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>275</v>
+      </c>
+      <c r="O35" t="s">
+        <v>276</v>
+      </c>
+      <c r="P35" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="13:18">
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>277</v>
+      </c>
+      <c r="O36" t="s">
+        <v>278</v>
+      </c>
+      <c r="P36" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="13:18">
+      <c r="M37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>279</v>
+      </c>
+      <c r="O37" t="s">
+        <v>280</v>
+      </c>
+      <c r="P37" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>35</v>
+      </c>
+      <c r="R37" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="13:18">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>281</v>
+      </c>
+      <c r="O38" t="s">
+        <v>282</v>
+      </c>
+      <c r="P38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="13:18">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>283</v>
+      </c>
+      <c r="O39" t="s">
+        <v>284</v>
+      </c>
+      <c r="P39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="13:18">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>285</v>
+      </c>
+      <c r="O40" t="s">
+        <v>286</v>
+      </c>
+      <c r="P40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>35</v>
+      </c>
+      <c r="R40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="13:18">
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>287</v>
+      </c>
+      <c r="O41" t="s">
+        <v>288</v>
+      </c>
+      <c r="P41" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>35</v>
+      </c>
+      <c r="R41" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="13:18">
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>289</v>
+      </c>
+      <c r="O42" t="s">
+        <v>290</v>
+      </c>
+      <c r="P42" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="13:18">
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>291</v>
+      </c>
+      <c r="O43" t="s">
+        <v>292</v>
+      </c>
+      <c r="P43" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>35</v>
+      </c>
+      <c r="R43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="13:18">
+      <c r="M44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>293</v>
+      </c>
+      <c r="O44" t="s">
+        <v>294</v>
+      </c>
+      <c r="P44" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>35</v>
+      </c>
+      <c r="R44" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="13:18">
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>295</v>
+      </c>
+      <c r="O45" t="s">
+        <v>296</v>
+      </c>
+      <c r="P45" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>35</v>
+      </c>
+      <c r="R45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="13:18">
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>297</v>
+      </c>
+      <c r="O46" t="s">
+        <v>298</v>
+      </c>
+      <c r="P46" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="13:18">
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>299</v>
+      </c>
+      <c r="O47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P47" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="13:18">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>301</v>
+      </c>
+      <c r="O48" t="s">
+        <v>302</v>
+      </c>
+      <c r="P48" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="13:18">
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>303</v>
+      </c>
+      <c r="O49" t="s">
+        <v>304</v>
+      </c>
+      <c r="P49" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="13:18">
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>305</v>
+      </c>
+      <c r="O50" t="s">
+        <v>306</v>
+      </c>
+      <c r="P50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="13:18">
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>307</v>
+      </c>
+      <c r="O51" t="s">
+        <v>308</v>
+      </c>
+      <c r="P51" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>35</v>
+      </c>
+      <c r="R51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="13:18">
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>309</v>
+      </c>
+      <c r="O52" t="s">
+        <v>310</v>
+      </c>
+      <c r="P52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>35</v>
+      </c>
+      <c r="R52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="M53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>311</v>
+      </c>
+      <c r="O53" t="s">
+        <v>312</v>
+      </c>
+      <c r="P53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>35</v>
+      </c>
+      <c r="R53" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="13:18">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>313</v>
+      </c>
+      <c r="O54" t="s">
+        <v>314</v>
+      </c>
+      <c r="P54" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>35</v>
+      </c>
+      <c r="R54" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="13:18">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>315</v>
+      </c>
+      <c r="O55" t="s">
+        <v>316</v>
+      </c>
+      <c r="P55" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="13:18">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>317</v>
+      </c>
+      <c r="O56" t="s">
+        <v>318</v>
+      </c>
+      <c r="P56" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R56" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="13:18">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>319</v>
+      </c>
+      <c r="O57" t="s">
+        <v>320</v>
+      </c>
+      <c r="P57" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="13:18">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>321</v>
+      </c>
+      <c r="O58" t="s">
+        <v>322</v>
+      </c>
+      <c r="P58" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="13:18">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>323</v>
+      </c>
+      <c r="O59" t="s">
+        <v>324</v>
+      </c>
+      <c r="P59" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="13:18">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>325</v>
+      </c>
+      <c r="O60" t="s">
+        <v>326</v>
+      </c>
+      <c r="P60" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>35</v>
+      </c>
+      <c r="R60" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>327</v>
+      </c>
+      <c r="O61" t="s">
+        <v>328</v>
+      </c>
+      <c r="P61" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>35</v>
+      </c>
+      <c r="R61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>329</v>
+      </c>
+      <c r="O62" t="s">
+        <v>330</v>
+      </c>
+      <c r="P62" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="13:18">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>331</v>
+      </c>
+      <c r="O63" t="s">
+        <v>332</v>
+      </c>
+      <c r="P63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="13:18">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>333</v>
+      </c>
+      <c r="O64" t="s">
+        <v>334</v>
+      </c>
+      <c r="P64" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="13:18">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>335</v>
+      </c>
+      <c r="O65" t="s">
+        <v>336</v>
+      </c>
+      <c r="P65" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>35</v>
+      </c>
+      <c r="R65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="13:18">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>337</v>
+      </c>
+      <c r="O66" t="s">
+        <v>338</v>
+      </c>
+      <c r="P66" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>35</v>
+      </c>
+      <c r="R66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="13:18">
+      <c r="M67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N67" t="s">
+        <v>339</v>
+      </c>
+      <c r="O67" t="s">
+        <v>340</v>
+      </c>
+      <c r="P67" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>35</v>
+      </c>
+      <c r="R67" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="68" spans="13:18">
+      <c r="M68" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>341</v>
+      </c>
+      <c r="O68" t="s">
+        <v>342</v>
+      </c>
+      <c r="P68" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>35</v>
+      </c>
+      <c r="R68" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
